--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-batterie-examen-et-surveillance-prenataux.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-batterie-examen-et-surveillance-prenataux.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2867" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Observation - Fr Observation Batterie Examens Et Surveillance Prenataux</t>
+    <t>Observation - Fr Batterie examens et surveillance prénataux</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,7 +647,7 @@
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
+    <t>Type de l'observation</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -856,379 +856,210 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur</t>
-  </si>
-  <si>
-    <t>auteur</t>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Auteur</t>
+  </si>
+  <si>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
 </t>
   </si>
   <si>
-    <t>Observation.performer:auteur.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction</t>
-  </si>
-  <si>
-    <t>performerFunction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {event-performerFunction}
-</t>
-  </si>
-  <si>
-    <t>Type of performance</t>
-  </si>
-  <si>
-    <t>Distinguishes the type of involvement of the performer in the event. For example, 'author',  'verifier' or 'responsible party'.</t>
-  </si>
-  <si>
-    <t>Event.performer.function</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.url</t>
+    <t>Observation.performer.extension:author.url</t>
   </si>
   <si>
     <t>Observation.performer.extension.url</t>
   </si>
   <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/event-performerFunction</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x]</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.value[x]</t>
   </si>
   <si>
     <t>Observation.performer.extension.value[x]</t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-function</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].coding</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.extension:performerFunction.value[x].text</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.reference</t>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>Observation.performer.reference</t>
@@ -1250,9 +1081,6 @@
 </t>
   </si>
   <si>
-    <t>Observation.performer:auteur.type</t>
-  </si>
-  <si>
     <t>Observation.performer.type</t>
   </si>
   <si>
@@ -1266,6 +1094,9 @@
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
@@ -1273,9 +1104,6 @@
   </si>
   <si>
     <t>Reference.type</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.identifier</t>
   </si>
   <si>
     <t>Observation.performer.identifier</t>
@@ -1297,9 +1125,6 @@
   </si>
   <si>
     <t>.identifier</t>
-  </si>
-  <si>
-    <t>Observation.performer:auteur.display</t>
   </si>
   <si>
     <t>Observation.performer.display</t>
@@ -2167,12 +1992,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP74"/>
+  <dimension ref="A1:AP77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="71.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.58203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="57.26171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.44921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2180,7 +2005,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.26171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2195,7 +2020,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.4296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4772,7 +4597,7 @@
         <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>82</v>
@@ -4828,14 +4653,16 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>262</v>
@@ -4853,19 +4680,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4873,14 +4700,12 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4889,7 +4714,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4898,21 +4723,19 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>266</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4960,34 +4783,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4995,21 +4818,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -5021,15 +4844,17 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5066,31 +4891,31 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5102,7 +4927,7 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5116,11 +4941,13 @@
         <v>283</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5139,17 +4966,15 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>139</v>
+        <v>285</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>140</v>
+        <v>286</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5186,19 +5011,19 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5222,7 +5047,7 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5233,14 +5058,12 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>290</v>
-      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5261,13 +5084,13 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5318,22 +5141,22 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
@@ -5342,7 +5165,7 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5353,10 +5176,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5364,10 +5187,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5379,13 +5202,13 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5424,31 +5247,31 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5460,7 +5283,7 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5471,21 +5294,23 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5500,10 +5325,10 @@
         <v>139</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5542,19 +5367,19 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5589,10 +5414,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5600,7 +5425,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
@@ -5615,24 +5440,22 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>272</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>82</v>
@@ -5674,10 +5497,10 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>93</v>
@@ -5698,7 +5521,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5709,10 +5532,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5720,10 +5543,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5735,13 +5558,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5768,41 +5591,43 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5814,7 +5639,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5825,10 +5650,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5836,7 +5661,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
@@ -5851,22 +5676,24 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>278</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>82</v>
@@ -5908,10 +5735,10 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>93</v>
@@ -5932,7 +5759,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>282</v>
+        <v>136</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5943,21 +5770,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5969,24 +5796,22 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -6004,43 +5829,41 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6052,7 +5875,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>282</v>
+        <v>136</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6063,12 +5886,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6077,7 +5902,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6086,23 +5911,19 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>323</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6150,7 +5971,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6162,7 +5983,7 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6171,10 +5992,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6185,10 +6006,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6211,13 +6032,13 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6268,7 +6089,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6292,7 +6113,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6303,21 +6124,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6332,14 +6153,12 @@
         <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6376,19 +6195,19 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6412,7 +6231,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6423,10 +6242,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6434,7 +6253,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
@@ -6446,29 +6265,27 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6510,10 +6327,10 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>93</v>
@@ -6522,7 +6339,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6531,10 +6348,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>343</v>
+        <v>136</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6545,10 +6362,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6568,20 +6385,18 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6630,7 +6445,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6651,10 +6466,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>351</v>
+        <v>136</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6665,18 +6480,20 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
@@ -6688,21 +6505,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>355</v>
+        <v>294</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>356</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6711,7 +6526,7 @@
         <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>82</v>
@@ -6750,19 +6565,19 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6771,10 +6586,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6785,10 +6600,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6808,21 +6623,19 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>363</v>
+        <v>273</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>364</v>
+        <v>274</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>365</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6870,7 +6683,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>275</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6882,7 +6695,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6891,10 +6704,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>276</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6905,10 +6718,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6919,7 +6732,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6928,23 +6741,19 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>371</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>372</v>
+        <v>293</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6980,31 +6789,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>376</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7013,10 +6822,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7027,10 +6836,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7038,7 +6847,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
@@ -7050,29 +6859,27 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>278</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>381</v>
+        <v>303</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>382</v>
+        <v>304</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>82</v>
@@ -7114,10 +6921,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>385</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -7126,7 +6933,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7135,10 +6942,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>387</v>
+        <v>136</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7149,10 +6956,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>388</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7172,20 +6979,18 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>390</v>
+        <v>309</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7234,7 +7039,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>393</v>
+        <v>313</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7243,7 +7048,7 @@
         <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
@@ -7269,10 +7074,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>395</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>396</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7280,7 +7085,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7292,19 +7097,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>397</v>
+        <v>303</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>398</v>
+        <v>304</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>399</v>
+        <v>305</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7312,7 +7117,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7330,13 +7135,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7354,10 +7159,10 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>402</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
@@ -7366,7 +7171,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7389,10 +7194,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>404</v>
+        <v>332</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7403,7 +7208,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7412,20 +7217,18 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>333</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>405</v>
+        <v>309</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7474,7 +7277,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7498,7 +7301,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>409</v>
+        <v>136</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7509,10 +7312,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7535,16 +7338,16 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>413</v>
+        <v>336</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>414</v>
+        <v>337</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7594,7 +7397,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>415</v>
+        <v>338</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7603,7 +7406,7 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
@@ -7629,10 +7432,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>416</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7655,20 +7458,18 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>417</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>418</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>419</v>
+        <v>342</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7692,13 +7493,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7716,7 +7517,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>416</v>
+        <v>347</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7725,7 +7526,7 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>105</v>
@@ -7734,27 +7535,27 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>425</v>
+        <v>136</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>427</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>427</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7774,23 +7575,21 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>428</v>
+        <v>349</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>429</v>
+        <v>350</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7814,13 +7613,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7838,7 +7637,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>427</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7847,7 +7646,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7859,10 +7658,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>435</v>
+        <v>353</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7873,21 +7672,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7896,23 +7695,21 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>438</v>
+        <v>355</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>439</v>
+        <v>356</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7936,13 +7733,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7960,13 +7757,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -7978,27 +7775,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>446</v>
+        <v>136</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>359</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>448</v>
+        <v>359</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8009,7 +7806,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8018,22 +7815,22 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>449</v>
+        <v>360</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>450</v>
+        <v>361</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>451</v>
+        <v>362</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>452</v>
+        <v>363</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>453</v>
+        <v>364</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8082,16 +7879,16 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>448</v>
+        <v>359</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -8100,27 +7897,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>454</v>
+        <v>367</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>455</v>
+        <v>368</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>456</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>456</v>
+        <v>370</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8146,15 +7943,17 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>457</v>
+        <v>371</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>458</v>
+        <v>372</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8178,13 +7977,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>207</v>
+        <v>344</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>460</v>
+        <v>375</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>461</v>
+        <v>376</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8202,7 +8001,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>456</v>
+        <v>370</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8211,7 +8010,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8220,38 +8019,38 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>462</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>463</v>
+        <v>136</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>466</v>
+        <v>379</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>466</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8266,16 +8065,16 @@
         <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>467</v>
+        <v>381</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>468</v>
+        <v>382</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>469</v>
+        <v>383</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>470</v>
+        <v>384</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8300,13 +8099,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>207</v>
+        <v>344</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>471</v>
+        <v>385</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>472</v>
+        <v>386</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8324,13 +8123,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>466</v>
+        <v>379</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8342,27 +8141,27 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>473</v>
+        <v>388</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>474</v>
+        <v>389</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>475</v>
+        <v>391</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>475</v>
+        <v>391</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8373,7 +8172,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8385,18 +8184,20 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>476</v>
+        <v>392</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>477</v>
+        <v>393</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>478</v>
+        <v>394</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8444,13 +8245,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>475</v>
+        <v>391</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8462,27 +8263,27 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>481</v>
+        <v>397</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>482</v>
+        <v>398</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>484</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>484</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8505,16 +8306,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>485</v>
+        <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>486</v>
+        <v>400</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>487</v>
+        <v>401</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>488</v>
+        <v>402</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8540,13 +8341,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8564,7 +8365,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>484</v>
+        <v>399</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8582,27 +8383,27 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>489</v>
+        <v>405</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>490</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>491</v>
+        <v>407</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>492</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8613,7 +8414,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8625,19 +8426,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>494</v>
+        <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>497</v>
+        <v>412</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8662,13 +8463,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8686,19 +8487,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>499</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8707,10 +8508,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>500</v>
+        <v>416</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>501</v>
+        <v>417</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8721,10 +8522,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8747,15 +8548,17 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>278</v>
+        <v>419</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>279</v>
+        <v>420</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8804,7 +8607,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>281</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8816,44 +8619,44 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>282</v>
+        <v>425</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8865,16 +8668,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>139</v>
+        <v>428</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>140</v>
+        <v>429</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>285</v>
+        <v>430</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>142</v>
+        <v>431</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8924,49 +8727,49 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>288</v>
+        <v>427</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>282</v>
+        <v>434</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8979,25 +8782,25 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>437</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>506</v>
+        <v>438</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>507</v>
+        <v>439</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>142</v>
+        <v>440</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>148</v>
+        <v>441</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9046,7 +8849,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>508</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9058,7 +8861,7 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>144</v>
+        <v>442</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9067,10 +8870,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>136</v>
+        <v>444</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9081,10 +8884,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>509</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>509</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9107,13 +8910,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>510</v>
+        <v>272</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>511</v>
+        <v>273</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>512</v>
+        <v>274</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9164,7 +8967,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>509</v>
+        <v>275</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9173,10 +8976,10 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9185,10 +8988,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>515</v>
+        <v>276</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9199,21 +9002,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9225,15 +9028,17 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>510</v>
+        <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>517</v>
+        <v>140</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9282,19 +9087,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>516</v>
+        <v>282</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9303,10 +9108,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>519</v>
+        <v>276</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9317,45 +9122,45 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>520</v>
+        <v>447</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>520</v>
+        <v>447</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>521</v>
+        <v>449</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>522</v>
+        <v>450</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>523</v>
+        <v>142</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>524</v>
+        <v>148</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9380,13 +9185,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9404,31 +9209,31 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>520</v>
+        <v>451</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>446</v>
+        <v>136</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9439,10 +9244,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>529</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>529</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9453,7 +9258,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9465,20 +9270,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>453</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>530</v>
+        <v>454</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9502,13 +9303,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9526,16 +9327,16 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>529</v>
+        <v>452</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9544,13 +9345,13 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>528</v>
+        <v>457</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9561,10 +9362,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>536</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>536</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9587,18 +9388,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>537</v>
+        <v>453</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>538</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>539</v>
+        <v>461</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>540</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9646,7 +9445,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>536</v>
+        <v>459</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9655,7 +9454,7 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9667,10 +9466,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>541</v>
+        <v>462</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9681,10 +9480,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>542</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>542</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9707,16 +9506,20 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>543</v>
+        <v>464</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9740,13 +9543,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9764,7 +9567,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>542</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9782,13 +9585,13 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>514</v>
+        <v>471</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>545</v>
+        <v>389</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9799,10 +9602,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>546</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>546</v>
+        <v>472</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9822,21 +9625,23 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>547</v>
+        <v>191</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>548</v>
+        <v>473</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>549</v>
+        <v>474</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9860,13 +9665,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9884,7 +9689,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>546</v>
+        <v>472</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9902,13 +9707,13 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>552</v>
+        <v>389</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9919,10 +9724,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>553</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>553</v>
+        <v>479</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9933,7 +9738,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9942,21 +9747,21 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>554</v>
+        <v>480</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>555</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10004,13 +9809,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>553</v>
+        <v>479</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10025,10 +9830,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>558</v>
+        <v>484</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10039,10 +9844,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>559</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>559</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10053,7 +9858,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10062,23 +9867,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>494</v>
+        <v>272</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>560</v>
+        <v>486</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10126,13 +9927,13 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>559</v>
+        <v>485</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
@@ -10147,10 +9948,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>564</v>
+        <v>457</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>565</v>
+        <v>488</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10161,10 +9962,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>566</v>
+        <v>489</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>566</v>
+        <v>489</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10175,7 +9976,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10184,18 +9985,20 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>278</v>
+        <v>490</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>279</v>
+        <v>491</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10244,19 +10047,19 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>281</v>
+        <v>489</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10265,10 +10068,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>282</v>
+        <v>495</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10279,14 +10082,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>567</v>
+        <v>496</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>567</v>
+        <v>496</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10302,19 +10105,19 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>139</v>
+        <v>497</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>140</v>
+        <v>498</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>285</v>
+        <v>499</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>142</v>
+        <v>500</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10364,7 +10167,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>288</v>
+        <v>496</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10376,7 +10179,7 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10385,10 +10188,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>282</v>
+        <v>501</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10399,14 +10202,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>568</v>
+        <v>502</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>568</v>
+        <v>502</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10416,28 +10219,28 @@
         <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>139</v>
+        <v>437</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10486,7 +10289,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10498,7 +10301,7 @@
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10507,10 +10310,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>136</v>
+        <v>508</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10521,10 +10324,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>569</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>569</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10532,35 +10335,31 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>570</v>
+        <v>273</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10584,13 +10383,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10608,10 +10407,10 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>569</v>
+        <v>275</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>93</v>
@@ -10620,22 +10419,22 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>213</v>
+        <v>276</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>82</v>
@@ -10643,46 +10442,44 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>574</v>
+        <v>510</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>574</v>
+        <v>510</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>417</v>
+        <v>139</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>575</v>
+        <v>140</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>419</v>
+        <v>278</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10730,80 +10527,80 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>574</v>
+        <v>282</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>425</v>
+        <v>276</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>578</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>578</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>581</v>
+        <v>142</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>431</v>
+        <v>148</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10828,13 +10625,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10852,19 +10649,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>578</v>
+        <v>451</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10873,10 +10670,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10887,45 +10684,45 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>582</v>
+        <v>512</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>582</v>
+        <v>512</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>438</v>
+        <v>513</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>439</v>
+        <v>514</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>440</v>
+        <v>515</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>441</v>
+        <v>205</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10950,13 +10747,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>313</v>
+        <v>207</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>442</v>
+        <v>208</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>443</v>
+        <v>209</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -10974,13 +10771,13 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>582</v>
+        <v>512</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
@@ -10992,27 +10789,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>444</v>
+        <v>516</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>445</v>
+        <v>212</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>446</v>
+        <v>213</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>583</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>583</v>
+        <v>517</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11023,31 +10820,31 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>584</v>
+        <v>518</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>585</v>
+        <v>362</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>498</v>
+        <v>364</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11096,13 +10893,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>583</v>
+        <v>517</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11114,23 +10911,389 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>500</v>
+        <v>367</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>501</v>
+        <v>368</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP74">
+  <autoFilter ref="A1:AP77">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11140,7 +11303,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI73">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-batterie-examen-et-surveillance-prenataux.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-batterie-examen-et-surveillance-prenataux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
